--- a/results/Int All Data -0.4/Rando_9_permute.xlsx
+++ b/results/Int All Data -0.4/Rando_9_permute.xlsx
@@ -440,1547 +440,1547 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.744233624814387</v>
+        <v>0.7280435938330676</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7414938862307283</v>
+        <v>0.7284414013089149</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7399897340006233</v>
+        <v>0.7220269849126473</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7408036810940622</v>
+        <v>0.7355405231993254</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7359383306751728</v>
+        <v>0.7355405231993254</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7452739738583658</v>
+        <v>0.7352481255385066</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7461511668408221</v>
+        <v>0.7399237382903444</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7442913710608811</v>
+        <v>0.737937450732369</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7419100258483198</v>
+        <v>0.7407560175255274</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7403187959449302</v>
+        <v>0.737621221287283</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7329428587141835</v>
+        <v>0.737621221287283</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7218949934920896</v>
+        <v>0.7384984142697391</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7113631780600927</v>
+        <v>0.7351766301857046</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7113631780600927</v>
+        <v>0.7342151093512255</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7095877101321748</v>
+        <v>0.7335670681405708</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.695594786338888</v>
+        <v>0.7326055473060917</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6837540559863609</v>
+        <v>0.7022401877211315</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6837540559863609</v>
+        <v>0.7022401877211315</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6849236466296358</v>
+        <v>0.7025325853819502</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6756906634402098</v>
+        <v>0.7005279656822306</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6935562521769418</v>
+        <v>0.7028882289317862</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6867651102678326</v>
+        <v>0.7019899539863241</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6815175346935782</v>
+        <v>0.6954490458120222</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6713468624539405</v>
+        <v>0.6936314139580928</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.674481658692185</v>
+        <v>0.693339016297274</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6834827402885479</v>
+        <v>0.6984995141982437</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6840730352527086</v>
+        <v>0.6965370584245357</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6845130066545675</v>
+        <v>0.6993822068232232</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6841573631047315</v>
+        <v>0.6946378485398449</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6841573631047315</v>
+        <v>0.6946378485398449</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6870813397129187</v>
+        <v>0.6940530532182074</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6744633265504409</v>
+        <v>0.6929412088214266</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6789097875304773</v>
+        <v>0.6854442794551687</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6688362756420833</v>
+        <v>0.685507525344186</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6722818016828906</v>
+        <v>0.6804102733322335</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6745999010064345</v>
+        <v>0.6825835487359988</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6745999010064345</v>
+        <v>0.6826046306990046</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6867834424095767</v>
+        <v>0.6881024400080662</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6774505490476452</v>
+        <v>0.6899228216832572</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6832352563750024</v>
+        <v>0.6899228216832572</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6777401968872023</v>
+        <v>0.6834185777924435</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6777401968872023</v>
+        <v>0.6898962400777283</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6774688811893894</v>
+        <v>0.705633467157968</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6768180901574731</v>
+        <v>0.7116949898256614</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6771315697812976</v>
+        <v>0.7090689105208161</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.6824341417807842</v>
+        <v>0.6914801371244202</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6712460356743478</v>
+        <v>0.6922519202918477</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6769280830079378</v>
+        <v>0.6806742561733488</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6742671726337788</v>
+        <v>0.6800683788887056</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6573154411629911</v>
+        <v>0.6708143137362739</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6649626940915507</v>
+        <v>0.6553062384278354</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.669324827219564</v>
+        <v>0.6634062952574749</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.6613640946671799</v>
+        <v>0.6600634292104346</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.6594804671029717</v>
+        <v>0.6693624081101395</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.6594804671029717</v>
+        <v>0.6740169388989716</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.644936662450274</v>
+        <v>0.6693202441841279</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.6463986507543675</v>
+        <v>0.6670443087865956</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.6461062530935489</v>
+        <v>0.6676923499972501</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.6531265467744597</v>
+        <v>0.6615025023373481</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.6359988267429284</v>
+        <v>0.6583172927093073</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.6423683293919229</v>
+        <v>0.6578984032704541</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.6459009331060148</v>
+        <v>0.6530275532090415</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.6572072815267007</v>
+        <v>0.6559093658912171</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.6576866670333095</v>
+        <v>0.6645419714385232</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.6589167537443399</v>
+        <v>0.6480540431538617</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.6558662853581184</v>
+        <v>0.6570001283249922</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.6473235073053585</v>
+        <v>0.6483858549194302</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.6431483620231351</v>
+        <v>0.6483858549194302</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.6469495316137784</v>
+        <v>0.6508964417312875</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.6540697354671947</v>
+        <v>0.6602348347357422</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.6422840015398998</v>
+        <v>0.6540495701112761</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.6183596399567362</v>
+        <v>0.6573081083062935</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.6236466296357404</v>
+        <v>0.6573081083062935</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.623061834314103</v>
+        <v>0.6598370272598948</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.6437331573447727</v>
+        <v>0.6598370272598948</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.6439833910795798</v>
+        <v>0.6607380520266183</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.6436488294927496</v>
+        <v>0.6582430475352435</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.6441914608883756</v>
+        <v>0.6597499495866102</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.6349529780564263</v>
+        <v>0.6415442996205247</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.6342811050615043</v>
+        <v>0.647792810134008</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.6323131496452731</v>
+        <v>0.669507232029918</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.633211424590735</v>
+        <v>0.674712643678161</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.6338383838383839</v>
+        <v>0.6678820876643019</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.6320601660892042</v>
+        <v>0.6741755119250582</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.6307219197418834</v>
+        <v>0.6751159507965315</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.6307219197418834</v>
+        <v>0.6675420264349484</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.6232039084126199</v>
+        <v>0.6585171130543181</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.6264230325028873</v>
+        <v>0.6558644521439441</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.6251901959705952</v>
+        <v>0.6558644521439441</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.617967332123412</v>
+        <v>0.6290078644888082</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.599608608773763</v>
+        <v>0.6340024565069937</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.5926909750866194</v>
+        <v>0.6078379072026985</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.6130011549249299</v>
+        <v>0.6085675264441145</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.6133146345487543</v>
+        <v>0.6170525582503804</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.612832499220884</v>
+        <v>0.6218601624227759</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.612832499220884</v>
+        <v>0.6357247612238538</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.6265513574950962</v>
+        <v>0.6208830592678143</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.6264276155383234</v>
+        <v>0.635116134117949</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.621477937267411</v>
+        <v>0.6348237364571303</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.6502172358796678</v>
+        <v>0.6348237364571303</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.6522640195053988</v>
+        <v>0.6299895506792058</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.6466901318080991</v>
+        <v>0.6234642248253863</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.6447881721021467</v>
+        <v>0.6266274358833342</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.6625593503088966</v>
+        <v>0.6191094245540707</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.6625593503088966</v>
+        <v>0.6297576490861427</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.6587554308969916</v>
+        <v>0.6297576490861427</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.659005664631799</v>
+        <v>0.6108856257676585</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.6544217125886818</v>
+        <v>0.5937634053786505</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.6559258648187868</v>
+        <v>0.5931575280940072</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.6432079414838036</v>
+        <v>0.598505013840767</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.6349722268052577</v>
+        <v>0.5955333736640451</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.638618489798163</v>
+        <v>0.6024088434251773</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.6014839868741866</v>
+        <v>0.5550101743386679</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.5647252928559644</v>
+        <v>0.5430979486333388</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5412546517809675</v>
+        <v>0.5432033584483675</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.5290921923408312</v>
+        <v>0.5222900511466755</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5285963079066527</v>
+        <v>0.5231672441291315</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.5185044638765147</v>
+        <v>0.4944554437294909</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5303516104786522</v>
+        <v>0.5054767273460559</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.5318612623512805</v>
+        <v>0.5114401730554181</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.5396166749161304</v>
+        <v>0.5216685915415498</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.5250279565161597</v>
+        <v>0.5189737667051642</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.5312682175658582</v>
+        <v>0.5220929806229262</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.5102064199160388</v>
+        <v>0.5375460595061321</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.5067792260169756</v>
+        <v>0.5336550624209426</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.4917844506773726</v>
+        <v>0.5370822563200058</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.4917844506773726</v>
+        <v>0.5370611743570002</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.4907596839538763</v>
+        <v>0.5448055876368036</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.488043777154485</v>
+        <v>0.5375084786155566</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.5068204733358999</v>
+        <v>0.5362389777997764</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5075079286513043</v>
+        <v>0.5341527800692955</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.5075079286513043</v>
+        <v>0.5368182734788906</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5081348878989532</v>
+        <v>0.54921263451209</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5086564373315734</v>
+        <v>0.5488991548882656</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.5065014940695521</v>
+        <v>0.5488991548882656</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.5052897395002658</v>
+        <v>0.5365680397440833</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.5011329263597866</v>
+        <v>0.5322664026838255</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.498037544226292</v>
+        <v>0.5414443894480192</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.4991860529065611</v>
+        <v>0.5393765238592825</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.4991860529065611</v>
+        <v>0.5536682615629984</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.4988936552457424</v>
+        <v>0.5543676327705366</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.4998340941172157</v>
+        <v>0.5604429045445379</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5001264917780345</v>
+        <v>0.5425800656290675</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.4998551760802215</v>
+        <v>0.5390557113787604</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5001897376670517</v>
+        <v>0.5468872023318485</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5005032172908761</v>
+        <v>0.5540752351097179</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.4991860529065611</v>
+        <v>0.5490934755907533</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.4988936552457424</v>
+        <v>0.5230013382463473</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.4982877779610992</v>
+        <v>0.5268419219417404</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.4983299418871107</v>
+        <v>0.5263176226878586</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.4983299418871107</v>
+        <v>0.5074914297237346</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.4986434215109351</v>
+        <v>0.5137958532695375</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.4992492987955783</v>
+        <v>0.5067022310216502</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.499270380758584</v>
+        <v>0.5001567398119122</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.4989358191717538</v>
+        <v>0.4950200736952098</v>
       </c>
     </row>
   </sheetData>
